--- a/Matriz_de_Evolucion_Operativa.xlsx
+++ b/Matriz_de_Evolucion_Operativa.xlsx
@@ -1982,17 +1982,17 @@
           <t>NyTEX Tesorería</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D14" s="33" t="n"/>
       <c r="E14" s="33" t="inlineStr">
         <is>
           <t>X</t>

--- a/Matriz_de_Evolucion_Operativa.xlsx
+++ b/Matriz_de_Evolucion_Operativa.xlsx
@@ -2035,7 +2035,11 @@
       </c>
       <c r="B16" s="33" t="n"/>
       <c r="C16" s="33" t="n"/>
-      <c r="D16" s="33" t="n"/>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
           <t>X</t>
